--- a/stakeholderMap.xlsx
+++ b/stakeholderMap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\papai.roland\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558CD9F6-B54E-4104-8CBF-F7DFFA9850A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3E6156-CA31-4FFE-8CA5-C5FDFEF688A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
   <si>
     <t>Kategória</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>Magas</t>
-  </si>
-  <si>
-    <t>Közepes</t>
   </si>
   <si>
     <t>Felel a folyamatért, a feladatok ütemezéséért (Backlog), a határidők betartásáért.</t>
@@ -121,7 +118,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,13 +167,6 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -255,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -272,31 +262,28 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -619,20 +606,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="A1" s="16"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
     </row>
     <row r="3" spans="1:6" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -668,31 +655,31 @@
       <c r="D5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>13</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -700,79 +687,79 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="7" t="s">
+    </row>
+    <row r="8" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="B8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="10" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="E9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="7" t="s">
+    </row>
+    <row r="10" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="B10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
